--- a/outputs_level2_aging_assets/aging_tables_for_word.xlsx
+++ b/outputs_level2_aging_assets/aging_tables_for_word.xlsx
@@ -1,45 +1,134 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Documents\rei\@SKRIPSHIT\PV_Smoothing_Skripsi\outputs_level2_aging_assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E29EC4B-0935-406C-87B5-49563E2D06C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Table_4_10_Mechanism" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Table_4_11_Synthesis" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Table_4_10_Mechanism" sheetId="1" r:id="rId1"/>
+    <sheet name="Table_4_11_Synthesis" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Throughput_act</t>
+  </si>
+  <si>
+    <t>Mismatch</t>
+  </si>
+  <si>
+    <t>fp</t>
+  </si>
+  <si>
+    <t>fsoc</t>
+  </si>
+  <si>
+    <t>soc_span_actual</t>
+  </si>
+  <si>
+    <t>n_cycles_total</t>
+  </si>
+  <si>
+    <t>damage_index</t>
+  </si>
+  <si>
+    <t>SMA</t>
+  </si>
+  <si>
+    <t>EMA</t>
+  </si>
+  <si>
+    <t>Hari</t>
+  </si>
+  <si>
+    <t>Kandidat damage minimum</t>
+  </si>
+  <si>
+    <t>Nilai damage minimum</t>
+  </si>
+  <si>
+    <t>Kandidat damage maksimum</t>
+  </si>
+  <si>
+    <t>Nilai damage maksimum</t>
+  </si>
+  <si>
+    <t>Pola utama</t>
+  </si>
+  <si>
+    <t>clear (2024-06-05)</t>
+  </si>
+  <si>
+    <t>SMA 60min large</t>
+  </si>
+  <si>
+    <t>SMA 10min large</t>
+  </si>
+  <si>
+    <t>Damage relatif paling rendah; horizon besar cenderung menurunkan damage.</t>
+  </si>
+  <si>
+    <t>medium (2025-03-15)</t>
+  </si>
+  <si>
+    <t>SMA 10min small</t>
+  </si>
+  <si>
+    <t>Damage cenderung turun saat horizon membesar; pengaruh metode tetap bergantung konteks.</t>
+  </si>
+  <si>
+    <t>cloudy (2024-04-03)</t>
+  </si>
+  <si>
+    <t>SMA 60min small</t>
+  </si>
+  <si>
+    <t>Damage relatif paling tinggi; constraint paling terasa dan damage tidak identik dengan throughput.</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D9EAF7"/>
+        <fgColor rgb="FFD9EAF7"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,82 +144,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -418,120 +454,95 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
-    <col width="7" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col min="1" max="1" width="8" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="5" width="7" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="16" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Method</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Throughput_act</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Mismatch</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>fp</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>fsoc</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>soc_span_actual</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>n_cycles_total</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>damage_index</t>
-        </is>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SMA</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
         <v>3559.549</v>
       </c>
-      <c r="C2" t="n">
-        <v>4782.972</v>
-      </c>
-      <c r="D2" t="n">
+      <c r="C2">
+        <v>4782.9719999999998</v>
+      </c>
+      <c r="D2">
         <v>0.51</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.231</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.281</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="E2">
+        <v>0.23100000000000001</v>
+      </c>
+      <c r="F2">
+        <v>0.28100000000000003</v>
+      </c>
+      <c r="G2">
         <v>38.5</v>
       </c>
-      <c r="H2" t="n">
-        <v>0.000457</v>
+      <c r="H2">
+        <v>4.57E-4</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>EMA</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>3428.979</v>
-      </c>
-      <c r="C3" t="n">
-        <v>4062.952</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.455</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.266</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.284</v>
-      </c>
-      <c r="G3" t="n">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>3428.9789999999998</v>
+      </c>
+      <c r="C3">
+        <v>4062.9520000000002</v>
+      </c>
+      <c r="D3">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="E3">
+        <v>0.26600000000000001</v>
+      </c>
+      <c r="F3">
+        <v>0.28399999999999997</v>
+      </c>
+      <c r="G3">
         <v>43.5</v>
       </c>
-      <c r="H3" t="n">
-        <v>0.000525</v>
+      <c r="H3">
+        <v>5.2499999999999997E-4</v>
       </c>
     </row>
   </sheetData>
@@ -540,136 +551,96 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F4"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="24" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
+    <col min="4" max="4" width="24" customWidth="1"/>
+    <col min="5" max="5" width="23" customWidth="1"/>
+    <col min="6" max="6" width="24" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hari</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Kandidat damage minimum</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Nilai damage minimum</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Kandidat damage maksimum</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Nilai damage maksimum</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Pola utama</t>
-        </is>
+    <row r="1" spans="1:6" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>clear (2024-06-05)</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>SMA 60min large</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>0.000189</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>SMA 10min large</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.000599</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Damage relatif paling rendah; horizon besar cenderung menurunkan damage.</t>
-        </is>
+    <row r="2" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="3">
+        <v>1.8900000000000001E-4</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" s="3">
+        <v>5.9900000000000003E-4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>medium (2025-03-15)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>SMA 60min large</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>0.000278</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>SMA 10min small</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.000785</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Damage cenderung turun saat horizon membesar; pengaruh metode tetap bergantung konteks.</t>
-        </is>
+    <row r="3" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3">
+        <v>2.7799999999999998E-4</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="3">
+        <v>7.85E-4</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>cloudy (2024-04-03)</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SMA 60min small</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>0.000457</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>SMA 10min small</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.0008140000000000001</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Damage relatif paling tinggi; constraint paling terasa dan damage tidak identik dengan throughput.</t>
-        </is>
+    <row r="4" spans="1:6" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" s="3">
+        <v>4.57E-4</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="3">
+        <v>8.1400000000000005E-4</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
